--- a/Analysis/Prompt_Ablation/prompt_ablation_bootstrap_ci.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_bootstrap_ci.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1386542815293522</v>
+        <v>0.1339031339031339</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06451847416501728</v>
+        <v>0.0586894586894587</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2138960613120553</v>
+        <v>0.2102564102564103</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1795072379149357</v>
+        <v>0.1863247863247863</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08708233664208422</v>
+        <v>0.09287749287749289</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2701084065905606</v>
+        <v>0.2786324786324786</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1872341412776441</v>
+        <v>0.1943019943019944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1168335510952637</v>
+        <v>0.1213675213675214</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2584030899946966</v>
+        <v>0.2660968660968661</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.3914529914529915</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3470085470085469</v>
+        <v>0.3384615384615385</v>
       </c>
       <c r="F5" t="n">
-        <v>0.452991452991453</v>
+        <v>0.444487179487179</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.388034188034188</v>
+        <v>0.3897435897435897</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3282051282051282</v>
+        <v>0.32991452991453</v>
       </c>
       <c r="F6" t="n">
         <v>0.4495726495726495</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.452991452991453</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4017094017094016</v>
+        <v>0.4085470085470085</v>
       </c>
       <c r="F7" t="n">
-        <v>0.505982905982906</v>
+        <v>0.5145299145299145</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.741880341880342</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6940170940170939</v>
+        <v>0.6854700854700854</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7880341880341878</v>
+        <v>0.7794871794871795</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7316239316239316</v>
+        <v>0.7282051282051282</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6752136752136751</v>
+        <v>0.6700854700854701</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7846153846153846</v>
+        <v>0.7811965811965812</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7658119658119658</v>
+        <v>0.7606837606837605</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7213675213675214</v>
+        <v>0.7162393162393164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8068376068376067</v>
+        <v>0.8017094017094016</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1604735729247736</v>
+        <v>0.166951566951567</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05833618864049837</v>
+        <v>0.06324786324786323</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2627456372694826</v>
+        <v>0.2706552706552706</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1804741544144793</v>
+        <v>0.1897435897435897</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0793000163468667</v>
+        <v>0.08603988603988605</v>
       </c>
       <c r="F12" t="n">
-        <v>0.281215818047596</v>
+        <v>0.2923076923076923</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.109306644736094</v>
+        <v>0.1168091168091168</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001786374850723435</v>
+        <v>0.007407407407407427</v>
       </c>
       <c r="F13" t="n">
-        <v>0.216057909253672</v>
+        <v>0.2262108262108262</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3948717948717949</v>
+        <v>0.3931623931623932</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3299145299145299</v>
+        <v>0.3282051282051282</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4598290598290598</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4051282051282051</v>
+        <v>0.4068376068376068</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3401709401709401</v>
+        <v>0.3401709401709402</v>
       </c>
       <c r="F15" t="n">
-        <v>0.47008547008547</v>
+        <v>0.4735042735042735</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3606837606837607</v>
       </c>
       <c r="E16" t="n">
         <v>0.2957264957264957</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4256410256410256</v>
+        <v>0.4273504273504273</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7008547008547008</v>
+        <v>0.6957264957264957</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6376068376068377</v>
+        <v>0.6324786324786325</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7641025641025641</v>
+        <v>0.7590170940170934</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7128205128205128</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6495726495726496</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7743589743589744</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6888888888888888</v>
+        <v>0.6837606837606837</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.6188034188034187</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7521367521367522</v>
+        <v>0.7487179487179487</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.04757544012981867</v>
+        <v>0.04615384615384614</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02589729052500946</v>
+        <v>-0.02678062678062679</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1195465214752026</v>
+        <v>0.1179487179487179</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.05635269486357059</v>
+        <v>0.06381766381766382</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01381764913206653</v>
+        <v>-0.005128205128205126</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1275209967475027</v>
+        <v>0.1344729344729345</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.06378597559579198</v>
+        <v>0.06324786324786325</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.006160583943279885</v>
+        <v>-0.006267806267806275</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1334686602268877</v>
+        <v>0.1327635327635328</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3572649572649572</v>
+        <v>0.3504273504273504</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.3042735042735042</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4051282051282051</v>
+        <v>0.3982905982905983</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.3196581196581197</v>
+        <v>0.3179487179487179</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2700854700854701</v>
+        <v>0.2683760683760684</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3675213675213675</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3435897435897436</v>
+        <v>0.3401709401709401</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2974358974358974</v>
+        <v>0.294017094017094</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3914529914529915</v>
+        <v>0.388034188034188</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6871794871794872</v>
+        <v>0.6820512820512821</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.6358974358974359</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7316239316239317</v>
+        <v>0.726538461538461</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6735042735042734</v>
+        <v>0.676923076923077</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6273504273504273</v>
+        <v>0.6307692307692307</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7196581196581195</v>
+        <v>0.7213675213675215</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.699145299145299</v>
+        <v>0.6957264957264958</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6512820512820513</v>
+        <v>0.6478632478632479</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7452991452991452</v>
+        <v>0.7418803418803418</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.01341909416365631</v>
+        <v>-0.01025641025641026</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.071230035174193</v>
+        <v>-0.06723646723646723</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04509767988574487</v>
+        <v>0.04900284900284899</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1251776258190101</v>
+        <v>0.1230769230769231</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05563608297852651</v>
+        <v>0.05242165242165242</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1948932923382182</v>
+        <v>0.1943019943019943</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.006382929361177939</v>
+        <v>0.01196581196581197</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.05526563257914428</v>
+        <v>-0.04843304843304844</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06769193691844291</v>
+        <v>0.07350427350427349</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>0.2957264957264957</v>
       </c>
       <c r="E32" t="n">
-        <v>0.252991452991453</v>
+        <v>0.2547008547008546</v>
       </c>
       <c r="F32" t="n">
         <v>0.3384615384615385</v>
@@ -1431,13 +1431,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2991452991452991</v>
+        <v>0.3094017094017094</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2512820512820513</v>
+        <v>0.2598290598290598</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3470085470085469</v>
+        <v>0.3572649572649572</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3418803418803418</v>
+        <v>0.3401709401709401</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2974358974358974</v>
+        <v>0.2957264957264957</v>
       </c>
       <c r="F34" t="n">
-        <v>0.388034188034188</v>
+        <v>0.3863247863247862</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1524,13 +1524,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.6273504273504273</v>
+        <v>0.6205128205128205</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5794871794871795</v>
+        <v>0.570940170940171</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6752136752136753</v>
+        <v>0.67008547008547</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.67008547008547</v>
+        <v>0.6683760683760683</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6256410256410256</v>
+        <v>0.6239316239316239</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7128205128205128</v>
+        <v>0.711111111111111</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2811619855261805</v>
+        <v>0.2757834757834758</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2090851208949373</v>
+        <v>0.203988603988604</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3528994411467929</v>
+        <v>0.3481481481481482</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2343490890339761</v>
+        <v>0.2393162393162394</v>
       </c>
       <c r="E39" t="n">
-        <v>0.148476131479479</v>
+        <v>0.1515669515669516</v>
       </c>
       <c r="F39" t="n">
-        <v>0.318622658650895</v>
+        <v>0.3270655270655271</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1648,13 +1648,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.4991452991452991</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4376068376068376</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5538461538461538</v>
+        <v>0.547008547008547</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>0.4444444444444445</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3863247863247864</v>
+        <v>0.387991452991453</v>
       </c>
       <c r="F41" t="n">
         <v>0.5008547008547009</v>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.8222222222222221</v>
+        <v>0.8153846153846154</v>
       </c>
       <c r="E42" t="n">
-        <v>0.782905982905983</v>
+        <v>0.7743589743589744</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8598290598290599</v>
+        <v>0.8529914529914531</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1741,13 +1741,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.7367521367521368</v>
+        <v>0.7316239316239317</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6837606837606838</v>
+        <v>0.6786324786324787</v>
       </c>
       <c r="F43" t="n">
-        <v>0.788034188034188</v>
+        <v>0.7829059829059829</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.2997610314676699</v>
+        <v>0.3014245014245014</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2027209562952749</v>
+        <v>0.2022792022792023</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3929219562202013</v>
+        <v>0.3948717948717949</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2869692994205</v>
+        <v>0.2968660968660968</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1930982245131027</v>
+        <v>0.2011396011396011</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3789898308278835</v>
+        <v>0.3891737891737891</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1834,13 +1834,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.4837606837606837</v>
+        <v>0.4769230769230769</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4170940170940172</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5487606837606832</v>
+        <v>0.5435897435897435</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1868,10 +1868,10 @@
         <v>0.4598290598290598</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3931623931623931</v>
+        <v>0.3931623931623932</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5282051282051282</v>
+        <v>0.5264957264957265</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.7726495726495728</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7145299145299145</v>
+        <v>0.7111111111111112</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8273504273504273</v>
+        <v>0.8239316239316239</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.2422428621396842</v>
+        <v>0.2512820512820512</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1637234207287898</v>
+        <v>0.1726495726495727</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3175723072798515</v>
+        <v>0.3264957264957265</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.2001927430678138</v>
+        <v>0.2125356125356126</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1283705589094608</v>
+        <v>0.1396011396011396</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2719243837913684</v>
+        <v>0.2837606837606838</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4752136752136752</v>
       </c>
       <c r="E52" t="n">
-        <v>0.411965811965812</v>
+        <v>0.4205128205128205</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5196581196581197</v>
+        <v>0.5282051282051282</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.388034188034188</v>
+        <v>0.4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3401709401709401</v>
+        <v>0.3521367521367521</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4376068376068376</v>
+        <v>0.4495726495726496</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.7675213675213676</v>
+        <v>0.7675213675213675</v>
       </c>
       <c r="E54" t="n">
         <v>0.7196581196581195</v>
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.1317908013669313</v>
+        <v>0.1350427350427351</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0623312543592805</v>
+        <v>0.06552706552706553</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1990287076420657</v>
+        <v>0.2034188034188034</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.2024402571251442</v>
+        <v>0.2011396011396011</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1253444955620097</v>
+        <v>0.1213675213675214</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2770538825858141</v>
+        <v>0.2775071225071223</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.4427350427350428</v>
+        <v>0.4376068376068377</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3931623931623931</v>
+        <v>0.388034188034188</v>
       </c>
       <c r="F58" t="n">
-        <v>0.494017094017094</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.4017094017094018</v>
+        <v>0.3948717948717949</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3504273504273504</v>
+        <v>0.3418803418803418</v>
       </c>
       <c r="F59" t="n">
-        <v>0.452991452991453</v>
+        <v>0.4461538461538462</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.7401709401709401</v>
+        <v>0.7299145299145298</v>
       </c>
       <c r="E60" t="n">
-        <v>0.6940170940170939</v>
+        <v>0.6820512820512821</v>
       </c>
       <c r="F60" t="n">
-        <v>0.782905982905983</v>
+        <v>0.7743589743589744</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.6888888888888888</v>
+        <v>0.6803418803418803</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6358974358974359</v>
+        <v>0.6273504273504273</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7418803418803418</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
